--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484133_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484133_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1612</v>
+        <v>5.8817</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8192</v>
+        <v>5.3714</v>
       </c>
       <c r="F2" t="n">
-        <v>0.342</v>
+        <v>0.5103</v>
       </c>
       <c r="G2" t="n">
         <v>7.0636</v>
@@ -610,13 +610,13 @@
         <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3072</v>
+        <v>-0.5867</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7369</v>
+        <v>0.2891</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0442</v>
+        <v>-0.8759</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0838</v>
+        <v>5.2931</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9347</v>
+        <v>4.4246</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1491</v>
+        <v>0.8686</v>
       </c>
       <c r="G3" t="n">
         <v>5.1086</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3287</v>
+        <v>-0.462</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4252</v>
+        <v>-0.0849</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0965</v>
+        <v>-0.3771</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9405</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3431</v>
+        <v>1.6733</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5661</v>
+        <v>1.0365</v>
       </c>
       <c r="F4" t="n">
-        <v>0.777</v>
+        <v>0.6368</v>
       </c>
       <c r="G4" t="n">
         <v>1.2808</v>
@@ -766,13 +766,13 @@
         <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6717</v>
+        <v>-0.3415</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.153</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0483</v>
+        <v>-0.1885</v>
       </c>
       <c r="V4" t="n">
         <v>0.3373</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>T. SARTOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.4068</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2321</v>
+        <v>-0.1382</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3416</v>
+        <v>0.5451</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3376</v>
+        <v>0.2612</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5796</v>
+        <v>-1.3557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.758</v>
+        <v>1.6169</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.7533</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2175</v>
+        <v>-1.3753</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7255</v>
+        <v>2.1286</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3946</v>
+        <v>-0.4921</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3621</v>
+        <v>0.0195</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0325</v>
+        <v>-0.5117</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1903</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1984</v>
+        <v>-2.9758</v>
       </c>
       <c r="R5" t="n">
         <v>1.3887</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4308</v>
+        <v>-0.0057</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4876</v>
+        <v>0.3458</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9184</v>
+        <v>-0.3515</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2065</v>
+        <v>1.7384</v>
       </c>
       <c r="W5" t="n">
+        <v>1.7384</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.2065</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SARTOR</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1302</v>
+        <v>0.3804</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3026</v>
+        <v>0.722</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4328</v>
+        <v>-0.3416</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2612</v>
+        <v>1.3376</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3557</v>
+        <v>0.5796</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6169</v>
+        <v>0.758</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7533</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3753</v>
+        <v>0.2175</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1286</v>
+        <v>0.7255</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4921</v>
+        <v>0.3946</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0195</v>
+        <v>0.3621</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5117</v>
+        <v>0.0325</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9758</v>
+        <v>-0.1984</v>
       </c>
       <c r="R6" t="n">
         <v>1.3887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2823</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1814</v>
+        <v>-0.0226</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4637</v>
+        <v>-0.9184</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7384</v>
+        <v>-1.2065</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4178</v>
+        <v>-0.8249</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.3457</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7036</v>
+        <v>-0.4792</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1018</v>
@@ -1000,13 +1000,13 @@
         <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5225</v>
+        <v>-0.9296</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3797</v>
+        <v>-0.0112</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1428</v>
+        <v>-0.9184</v>
       </c>
       <c r="V7" t="n">
         <v>0.6032</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.824</v>
+        <v>-1.518</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4291</v>
+        <v>-2.123</v>
       </c>
       <c r="F8" t="n">
         <v>0.605</v>
@@ -1078,10 +1078,10 @@
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7799</v>
+        <v>-1.4738</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9352</v>
+        <v>-0.6291</v>
       </c>
       <c r="U8" t="n">
         <v>-0.8447</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4345</v>
+        <v>-1.9244</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4424</v>
+        <v>-2.9322</v>
       </c>
       <c r="F9" t="n">
         <v>1.0079</v>
@@ -1156,10 +1156,10 @@
         <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.213</v>
+        <v>-0.7029</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1846</v>
+        <v>-0.6744</v>
       </c>
       <c r="U9" t="n">
         <v>-0.0284</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.988</v>
+        <v>-4.1119</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1555</v>
+        <v>-3.1952</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8325</v>
+        <v>-0.9167</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8663</v>
@@ -1234,13 +1234,13 @@
         <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>0.267</v>
+        <v>0.1431</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2438</v>
+        <v>0.2041</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0232</v>
+        <v>-0.061</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.944600000000001</v>
+        <v>5.2561</v>
       </c>
       <c r="E11" t="n">
-        <v>2.508300000000001</v>
+        <v>2.8202</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4361</v>
+        <v>2.4362</v>
       </c>
       <c r="G11" t="n">
         <v>10.1788</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.687900000000001</v>
+        <v>-4.6879</v>
       </c>
       <c r="I11" t="n">
         <v>14.8668</v>
@@ -1312,13 +1312,13 @@
         <v>12.8951</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.6117</v>
+        <v>-5.3001</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0481</v>
+        <v>-0.7362000000000002</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.5638</v>
+        <v>-4.5639</v>
       </c>
       <c r="V11" t="n">
         <v>3.3533</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.3003</v>
+        <v>5.2091</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2726</v>
+        <v>5.1059</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0277</v>
+        <v>0.1033</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3328</v>
+        <v>2.6372</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3786</v>
+        <v>4.999</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7114</v>
+        <v>-2.3619</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0374</v>
+        <v>3.7835</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5179</v>
+        <v>3.8912</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5195</v>
+        <v>-0.1077</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2954</v>
+        <v>-1.1463</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8965</v>
+        <v>1.1079</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1918</v>
+        <v>-2.2542</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3887</v>
+        <v>2.579</v>
       </c>
       <c r="S12" t="n">
-        <v>5.0379</v>
+        <v>0.6476</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8375</v>
+        <v>0.5046</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2004</v>
+        <v>0.143</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2065</v>
+        <v>0.3373</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4724</v>
+        <v>1.8097</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7627</v>
+        <v>3.3568</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7998</v>
+        <v>1.7218</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.037</v>
+        <v>1.6349</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6372</v>
+        <v>-1.3328</v>
       </c>
       <c r="H13" t="n">
-        <v>4.999</v>
+        <v>0.3786</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.3619</v>
+        <v>-1.7114</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7835</v>
+        <v>-1.0374</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8912</v>
+        <v>-0.5179</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1077</v>
+        <v>-0.5195</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1463</v>
+        <v>-0.2954</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1079</v>
+        <v>0.8965</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.2542</v>
+        <v>-1.1918</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.579</v>
+        <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2013</v>
+        <v>2.0944</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1985</v>
+        <v>1.2868</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0027</v>
+        <v>0.8076</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3373</v>
+        <v>1.2065</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8097</v>
+        <v>1.4724</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7045</v>
+        <v>1.5948</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9856</v>
+        <v>1.6795</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2811</v>
+        <v>-0.0847</v>
       </c>
       <c r="G14" t="n">
         <v>1.6691</v>
@@ -1546,13 +1546,13 @@
         <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>0.25</v>
+        <v>0.1403</v>
       </c>
       <c r="T14" t="n">
-        <v>0.873</v>
+        <v>0.5669</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.623</v>
+        <v>-0.4266</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2065</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2755</v>
+        <v>0.7219</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2608</v>
+        <v>1.5669</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9853</v>
+        <v>-0.845</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7816</v>
@@ -1624,13 +1624,13 @@
         <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3315</v>
+        <v>0.1148</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0567</v>
+        <v>0.3628</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3883</v>
+        <v>-0.248</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.5071</v>
+        <v>-0.2475</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.0105</v>
+        <v>1.0558</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5034</v>
+        <v>-1.3033</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2541</v>
+        <v>5.1057</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5894</v>
+        <v>1.8345</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6647</v>
+        <v>3.2712</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4688</v>
+        <v>5.8027</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6696</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2008</v>
+        <v>4.8647</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7853</v>
+        <v>-0.697</v>
       </c>
       <c r="N16" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.8965</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8655</v>
+        <v>-1.5935</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7935</v>
+        <v>-2.579</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0465</v>
+        <v>0.6505</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5498</v>
+        <v>0.2325</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5032</v>
+        <v>0.418</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-3.4247</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-1.0118</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5764</v>
+        <v>-1.0836</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0355</v>
+        <v>-1.1942</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6119</v>
+        <v>0.1106</v>
       </c>
       <c r="G17" t="n">
-        <v>5.1057</v>
+        <v>-2.2541</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8345</v>
+        <v>-0.5894</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2712</v>
+        <v>-1.6647</v>
       </c>
       <c r="J17" t="n">
-        <v>5.8027</v>
+        <v>-0.4688</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9379999999999999</v>
+        <v>-0.6696</v>
       </c>
       <c r="L17" t="n">
-        <v>4.8647</v>
+        <v>0.2008</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.697</v>
+        <v>-1.7853</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8965</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5935</v>
+        <v>-1.8655</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.579</v>
+        <v>0.7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9677</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6784</v>
+        <v>0.3769</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7877999999999999</v>
+        <v>0.2665</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1093</v>
+        <v>0.1105</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.4247</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.0118</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9599</v>
+        <v>-1.9956</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9868</v>
+        <v>-1.1908</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9731</v>
+        <v>-0.8047</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4661</v>
@@ -1858,13 +1858,13 @@
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0294</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6122</v>
+        <v>0.4082</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6417</v>
+        <v>-0.4733</v>
       </c>
       <c r="V18" t="n">
         <v>-0.266</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1803</v>
+        <v>-2.3588</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1569</v>
+        <v>-2.0549</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0234</v>
+        <v>-0.3039</v>
       </c>
       <c r="G19" t="n">
         <v>-4.7921</v>
@@ -1936,13 +1936,13 @@
         <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9409</v>
+        <v>0.7624</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2495</v>
+        <v>0.3516</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6914</v>
+        <v>0.4108</v>
       </c>
       <c r="V19" t="n">
         <v>1.4724</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9667</v>
+        <v>-3.3367</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6605</v>
+        <v>-1.9462</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3062</v>
+        <v>-1.3904</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4434</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1185</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5498</v>
+        <v>0.1644</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4313</v>
+        <v>0.3471</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.7973</v>
+        <v>-6.805</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.9757</v>
+        <v>-7.1798</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1784</v>
+        <v>0.3748</v>
       </c>
       <c r="G21" t="n">
         <v>-6.5206</v>
@@ -2092,13 +2092,13 @@
         <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3861</v>
+        <v>0.3784</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6236</v>
+        <v>0.4195</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2375</v>
+        <v>-0.0412</v>
       </c>
       <c r="V21" t="n">
         <v>-0.266</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.944700000000001</v>
+        <v>-4.944599999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4361</v>
+        <v>-2.436000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.508500000000001</v>
+        <v>-2.5084</v>
       </c>
       <c r="G22" t="n">
         <v>-10.1787</v>
@@ -2170,13 +2170,13 @@
         <v>15.8708</v>
       </c>
       <c r="S22" t="n">
-        <v>5.611899999999999</v>
+        <v>5.6118</v>
       </c>
       <c r="T22" t="n">
-        <v>4.5636</v>
+        <v>4.5638</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0478</v>
+        <v>1.0479</v>
       </c>
       <c r="V22" t="n">
         <v>-3.3535</v>
